--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C68D55E-2450-4962-A578-1B3977ABD031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F644D1F-9231-4B0D-ACF4-5DA722F2D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="217">
   <si>
     <t>S.No.</t>
   </si>
@@ -685,6 +685,9 @@
   </si>
   <si>
     <t>608268-005-0204516</t>
+  </si>
+  <si>
+    <t>410751 - 411500</t>
   </si>
 </sst>
 </file>
@@ -1474,10 +1477,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I37" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A2:I37" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I37">
-    <sortCondition ref="H2:H37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I39" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="A2:I39" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I39">
+    <sortCondition ref="H2:H39"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
@@ -1880,7 +1883,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:AA39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1950,7 +1953,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A37" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A39" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2798,27 +2801,61 @@
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>35</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="7">
-        <f>SUM(C4:C30)</f>
-        <v>4447</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="7">
-        <f>SUM(F3:F36)</f>
-        <v>3942</v>
-      </c>
+      <c r="B37" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="4">
+        <v>750</v>
+      </c>
+      <c r="D37" s="5">
+        <v>46273</v>
+      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="5"/>
       <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <f>ROW()-2</f>
+        <v>36</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="7">
+        <f>SUM(C3:C38)</f>
+        <v>5947</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" s="7">
+        <f>SUM(F3:F38)</f>
+        <v>3942</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F644D1F-9231-4B0D-ACF4-5DA722F2D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33737C00-A4B0-4716-8400-B95F2DC944C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="222">
   <si>
     <t>S.No.</t>
   </si>
@@ -688,6 +688,21 @@
   </si>
   <si>
     <t>410751 - 411500</t>
+  </si>
+  <si>
+    <t>410751 - 411000</t>
+  </si>
+  <si>
+    <t>411001 - 411250</t>
+  </si>
+  <si>
+    <t>Order 9</t>
+  </si>
+  <si>
+    <t>608268-005-0246763</t>
+  </si>
+  <si>
+    <t>608268-005-0246614</t>
   </si>
 </sst>
 </file>
@@ -814,13 +829,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -946,6 +961,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1306,163 +1478,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1477,42 +1492,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I39" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A2:I39" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I39">
-    <sortCondition ref="H2:H39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I42" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:I42" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
+    <sortCondition ref="H2:H42"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H56" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H56" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:H56" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1883,7 +1898,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1910,17 +1925,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1953,7 +1968,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A39" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A42" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2813,10 +2828,18 @@
       <c r="D37" s="5">
         <v>46273</v>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="5"/>
+      <c r="E37" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F37" s="4">
+        <v>250</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="5">
+        <v>46277</v>
+      </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2827,35 +2850,85 @@
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="5"/>
+      <c r="E38" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="F38" s="4">
+        <v>250</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="5">
+        <v>46277</v>
+      </c>
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>37</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="7">
-        <f>SUM(C3:C38)</f>
-        <v>5947</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F39" s="7">
-        <f>SUM(F3:F38)</f>
-        <v>3942</v>
-      </c>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="5"/>
       <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <f>ROW()-2</f>
+        <v>38</v>
+      </c>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <f>ROW()-2</f>
+        <v>39</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="7">
+        <f>SUM(C3:C38)</f>
+        <v>5947</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" s="7">
+        <f>SUM(F3:F41)</f>
+        <v>4442</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2883,16 +2956,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -4277,12 +4350,24 @@
         <f>ROW()-2</f>
         <v>53</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="5"/>
+      <c r="B55" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="4">
+        <v>150</v>
+      </c>
+      <c r="G55" s="5">
+        <v>46277</v>
+      </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -4297,8 +4382,8 @@
         <v>153</v>
       </c>
       <c r="F56" s="7">
-        <f>SUM(F3:F54)</f>
-        <v>3464</v>
+        <f>SUM(F3:F55)</f>
+        <v>3614</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33737C00-A4B0-4716-8400-B95F2DC944C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42B0CA1-9E2B-43BD-AA97-A0E11CB364B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="221">
   <si>
     <t>S.No.</t>
   </si>
@@ -682,9 +682,6 @@
   </si>
   <si>
     <t>372901 - 3723000</t>
-  </si>
-  <si>
-    <t>608268-005-0204516</t>
   </si>
   <si>
     <t>410751 - 411500</t>
@@ -829,13 +826,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -961,6 +958,364 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1120,364 +1475,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1492,42 +1489,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I42" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I42" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A2:I42" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="H2:H42"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H56" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="A2:H56" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H55" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:H55" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1925,17 +1922,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2820,7 +2817,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C37" s="4">
         <v>750</v>
@@ -2829,7 +2826,7 @@
         <v>46273</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F37" s="4">
         <v>250</v>
@@ -2851,7 +2848,7 @@
       <c r="C38" s="4"/>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F38" s="4">
         <v>250</v>
@@ -2945,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2956,16 +2953,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -3496,7 +3493,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A56" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A55" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4326,70 +4323,45 @@
         <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="F54" s="4">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="G54" s="5">
-        <v>46267</v>
+        <v>46277</v>
       </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="4">
-        <v>150</v>
-      </c>
-      <c r="G55" s="5">
-        <v>46277</v>
-      </c>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F55" s="7">
+        <f>SUM(F3:F54)</f>
+        <v>3594</v>
+      </c>
+      <c r="G55" s="4"/>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
-        <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" s="7">
-        <f>SUM(F3:F55)</f>
-        <v>3614</v>
-      </c>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="8"/>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C56" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42B0CA1-9E2B-43BD-AA97-A0E11CB364B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4601F22-C42D-42CD-874C-070E560F5B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="225">
   <si>
     <t>S.No.</t>
   </si>
@@ -700,6 +700,18 @@
   </si>
   <si>
     <t>608268-005-0246614</t>
+  </si>
+  <si>
+    <t>608268-005-0246764</t>
+  </si>
+  <si>
+    <t>608268-005-0246913</t>
+  </si>
+  <si>
+    <t>608268-005-0246914</t>
+  </si>
+  <si>
+    <t>608268-005-0247113</t>
   </si>
 </sst>
 </file>
@@ -1512,8 +1524,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H55" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
-  <autoFilter ref="A2:H55" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H60" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:H60" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -2942,7 +2954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3493,7 +3505,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A55" si="1">ROW()-2</f>
+        <f t="shared" ref="A22:A60" si="1">ROW()-2</f>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4344,24 +4356,113 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
+        <f>ROW()-2</f>
+        <v>53</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="4">
+        <v>150</v>
+      </c>
+      <c r="G55" s="5">
+        <v>46277</v>
+      </c>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <f>ROW()-2</f>
+        <v>54</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F56" s="4">
+        <v>200</v>
+      </c>
+      <c r="G56" s="5">
+        <v>46277</v>
+      </c>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <f>ROW()-2</f>
+        <v>55</v>
+      </c>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <f>ROW()-2</f>
+        <v>56</v>
+      </c>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <f>ROW()-2</f>
+        <v>57</v>
+      </c>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
         <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F55" s="7">
-        <f>SUM(F3:F54)</f>
-        <v>3594</v>
-      </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C56" s="8"/>
+      <c r="F60" s="7">
+        <f>SUM(F3:F56)</f>
+        <v>3944</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C61" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4601F22-C42D-42CD-874C-070E560F5B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1783591-731B-48E6-BE59-559679E11DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="224">
   <si>
     <t>S.No.</t>
   </si>
@@ -691,9 +691,6 @@
   </si>
   <si>
     <t>411001 - 411250</t>
-  </si>
-  <si>
-    <t>Order 9</t>
   </si>
   <si>
     <t>608268-005-0246763</t>
@@ -1526,6 +1523,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H60" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:H60" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H60">
+    <sortCondition ref="D2:D60"/>
+  </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A20" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A34" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -3243,52 +3243,52 @@
         <v>10</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G12" s="5">
-        <v>46025</v>
+        <v>46062</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F13" s="4">
         <v>100</v>
       </c>
       <c r="G13" s="5">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3297,25 +3297,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>17</v>
+      <c r="E14" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G14" s="5">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3324,25 +3324,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F15" s="4">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="G15" s="5">
-        <v>46042</v>
+        <v>46026</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3351,25 +3351,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F16" s="4">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G16" s="5">
-        <v>46032</v>
+        <v>46042</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3378,25 +3378,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F17" s="4">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="G17" s="5">
-        <v>46042</v>
+        <v>46032</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3405,25 +3405,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F18" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G18" s="5">
-        <v>46032</v>
+        <v>46042</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -3432,24 +3432,26 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F19" s="4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G19" s="5">
-        <v>46031</v>
-      </c>
-      <c r="H19" s="4"/>
+        <v>46032</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
@@ -3457,30 +3459,28 @@
         <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G20" s="5">
-        <v>46062</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>46031</v>
+      </c>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -3505,7 +3505,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" ref="A22:A60" si="1">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3530,7 +3530,7 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -3580,7 +3580,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -3605,7 +3605,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -3632,7 +3632,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -3657,7 +3657,7 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -3707,7 +3707,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -3732,7 +3732,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -3757,7 +3757,7 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -3767,7 +3767,7 @@
         <v>132</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>16</v>
@@ -3784,7 +3784,7 @@
     </row>
     <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -3794,7 +3794,7 @@
         <v>134</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>17</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -3819,7 +3819,7 @@
         <v>137</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>13</v>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A35:A60" si="1">ROW()-2</f>
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -3846,7 +3846,7 @@
         <v>150</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>16</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -3873,7 +3873,7 @@
         <v>152</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>16</v>
@@ -3900,7 +3900,7 @@
         <v>162</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>17</v>
@@ -3927,7 +3927,7 @@
         <v>155</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>16</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <f t="shared" ref="A39:A44" si="2">ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -3954,7 +3954,7 @@
         <v>157</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>16</v>
@@ -3971,104 +3971,100 @@
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F40" s="4">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="G40" s="5">
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="4">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G41" s="5">
-        <v>46196</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>170</v>
-      </c>
+        <v>46205</v>
+      </c>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F42" s="4">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G42" s="5">
         <v>46205</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>201</v>
-      </c>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F43" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5">
         <v>46205</v>
@@ -4077,23 +4073,23 @@
     </row>
     <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F44" s="4">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="G44" s="5">
         <v>46205</v>
@@ -4102,23 +4098,23 @@
     </row>
     <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <f t="shared" ref="A45:A52" si="3">ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F45" s="4">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G45" s="5">
         <v>46205</v>
@@ -4127,23 +4123,23 @@
     </row>
     <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F46" s="4">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G46" s="5">
         <v>46205</v>
@@ -4152,23 +4148,23 @@
     </row>
     <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="4">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5">
         <v>46205</v>
@@ -4177,116 +4173,118 @@
     </row>
     <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>173</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F48" s="4">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="G48" s="5">
-        <v>46205</v>
+        <v>46227</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>173</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F49" s="4">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="G49" s="5">
-        <v>46205</v>
-      </c>
-      <c r="H49" s="4"/>
+        <v>46253</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="F50" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G50" s="5">
-        <v>46227</v>
+        <v>46262</v>
       </c>
       <c r="H50" s="4"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="F51" s="4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G51" s="5">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>202</v>
@@ -4295,59 +4293,57 @@
         <v>17</v>
       </c>
       <c r="F52" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G52" s="5">
-        <v>46262</v>
+        <v>46277</v>
       </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>202</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="F53" s="4">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G53" s="5">
-        <v>46262</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>161</v>
-      </c>
+        <v>46277</v>
+      </c>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F54" s="4">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G54" s="5">
         <v>46277</v>
@@ -4356,57 +4352,61 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F55" s="4">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="G55" s="5">
-        <v>46277</v>
-      </c>
-      <c r="H55" s="4"/>
+        <v>46196</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="F56" s="4">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="G56" s="5">
-        <v>46277</v>
-      </c>
-      <c r="H56" s="4"/>
+        <v>46196</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="B57" s="6"/>
@@ -4419,7 +4419,7 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B58" s="6"/>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="B59" s="6"/>

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1783591-731B-48E6-BE59-559679E11DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA0695D-793D-475C-A143-462995E6EA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="231">
   <si>
     <t>S.No.</t>
   </si>
@@ -709,6 +709,27 @@
   </si>
   <si>
     <t>608268-005-0247113</t>
+  </si>
+  <si>
+    <t>608268-005-0384914</t>
+  </si>
+  <si>
+    <t>608268-005-0385013</t>
+  </si>
+  <si>
+    <t>Order 9</t>
+  </si>
+  <si>
+    <t>608268-005-0385014</t>
+  </si>
+  <si>
+    <t>608268-005-0385063</t>
+  </si>
+  <si>
+    <t>608268-005-0384814</t>
+  </si>
+  <si>
+    <t>608268-005-0384913</t>
   </si>
 </sst>
 </file>
@@ -1521,10 +1542,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H60" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
-  <autoFilter ref="A2:H60" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H60">
-    <sortCondition ref="D2:D60"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:H63" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H63">
+    <sortCondition ref="D2:D63"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
@@ -2954,7 +2975,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B532C1-7F8B-4592-901A-51A1E632DC96}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultColWidth="37.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3836,7 +3857,7 @@
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
-        <f t="shared" ref="A35:A60" si="1">ROW()-2</f>
+        <f t="shared" ref="A35:A63" si="1">ROW()-2</f>
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -4409,12 +4430,24 @@
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="5"/>
+      <c r="B57" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4">
+        <v>100</v>
+      </c>
+      <c r="G57" s="5">
+        <v>46300</v>
+      </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -4422,11 +4455,21 @@
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="B58" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="4">
+        <v>50</v>
+      </c>
       <c r="G58" s="5"/>
       <c r="H58" s="4"/>
     </row>
@@ -4435,34 +4478,83 @@
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="B59" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="4">
+        <v>100</v>
+      </c>
       <c r="G59" s="5"/>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <f t="shared" si="1"/>
+        <f>ROW()-2</f>
         <v>58</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
       <c r="D60" s="6"/>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <f>ROW()-2</f>
+        <v>59</v>
+      </c>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <f>ROW()-2</f>
+        <v>60</v>
+      </c>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="F60" s="7">
-        <f>SUM(F3:F56)</f>
-        <v>3944</v>
-      </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="8"/>
+      <c r="F63" s="7">
+        <f>SUM(F3:F59)</f>
+        <v>4194</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C64" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA0695D-793D-475C-A143-462995E6EA24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6509F4-FF0F-42E1-A9E9-B6EC1E5048C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="234">
   <si>
     <t>S.No.</t>
   </si>
@@ -730,6 +730,15 @@
   </si>
   <si>
     <t>608268-005-0384913</t>
+  </si>
+  <si>
+    <t>411451 - 411500</t>
+  </si>
+  <si>
+    <t>411401 - 411450</t>
+  </si>
+  <si>
+    <t>411251 - 411400</t>
   </si>
 </sst>
 </file>
@@ -1519,10 +1528,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I42" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A2:I42" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
-    <sortCondition ref="H2:H42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I45" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="A2:I45" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I45">
+    <sortCondition ref="H2:H45"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
@@ -1928,7 +1937,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1998,7 +2007,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A42" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A45" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2902,10 +2911,18 @@
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="5"/>
+      <c r="E39" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="4">
+        <v>50</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H39" s="5">
+        <v>46309</v>
+      </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2916,10 +2933,18 @@
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="5"/>
+      <c r="E40" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F40" s="4">
+        <v>50</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="5">
+        <v>46309</v>
+      </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2930,35 +2955,87 @@
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="5"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F41" s="4">
+        <v>150</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="5">
+        <v>46309</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>40</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" s="7">
-        <f>SUM(C3:C38)</f>
-        <v>5947</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" s="7">
-        <f>SUM(F3:F41)</f>
-        <v>4442</v>
-      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <f>ROW()-2</f>
+        <v>41</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <f>ROW()-2</f>
+        <v>42</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="7">
+        <f>SUM(C3:C38)</f>
+        <v>5947</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F45" s="7">
+        <f>SUM(F3:F41)</f>
+        <v>4692</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6509F4-FF0F-42E1-A9E9-B6EC1E5048C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096B3D04-B880-4F26-9F06-352E5DA440F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="235">
   <si>
     <t>S.No.</t>
   </si>
@@ -739,6 +739,9 @@
   </si>
   <si>
     <t>411251 - 411400</t>
+  </si>
+  <si>
+    <t>Faizan Driver</t>
   </si>
 </sst>
 </file>
@@ -865,13 +868,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -997,6 +1000,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1357,163 +1517,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1528,45 +1531,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I45" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I45" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:I45" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I45">
     <sortCondition ref="H2:H45"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:H63" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H63">
     <sortCondition ref="D2:D63"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1964,17 +1967,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2855,7 +2858,7 @@
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A37:A44" si="4">ROW()-2</f>
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -2883,7 +2886,7 @@
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="B38" s="4"/>
@@ -2905,7 +2908,7 @@
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>37</v>
       </c>
       <c r="B39" s="4"/>
@@ -2927,7 +2930,7 @@
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="B40" s="4"/>
@@ -2945,11 +2948,13 @@
       <c r="H40" s="5">
         <v>46309</v>
       </c>
-      <c r="I40" s="4"/>
+      <c r="I40" s="4" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>39</v>
       </c>
       <c r="B41" s="4"/>
@@ -2973,7 +2978,7 @@
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="B42" s="4"/>
@@ -2987,7 +2992,7 @@
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="B43" s="4"/>
@@ -3001,7 +3006,7 @@
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
-        <f>ROW()-2</f>
+        <f t="shared" si="4"/>
         <v>42</v>
       </c>
       <c r="B44" s="4"/>
@@ -3063,16 +3068,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096B3D04-B880-4F26-9F06-352E5DA440F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAC9F5-E0F4-49A1-9669-8656C405D553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="RC" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="239">
   <si>
     <t>S.No.</t>
   </si>
@@ -742,6 +742,18 @@
   </si>
   <si>
     <t>Faizan Driver</t>
+  </si>
+  <si>
+    <t>540251 - 540500</t>
+  </si>
+  <si>
+    <t>540251 - 540300</t>
+  </si>
+  <si>
+    <t>540301 - 540330</t>
+  </si>
+  <si>
+    <t>540331 - 540500</t>
   </si>
 </sst>
 </file>
@@ -868,13 +880,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1000,6 +1012,364 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1159,364 +1529,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1531,45 +1543,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I45" headerRowDxfId="66" dataDxfId="65">
-  <autoFilter ref="A2:I45" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I45">
-    <sortCondition ref="H2:H45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I47" headerRowDxfId="56" dataDxfId="55">
+  <autoFilter ref="A2:I47" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I47">
+    <sortCondition ref="H2:H47"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A2:H63" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H63">
     <sortCondition ref="D2:D63"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1940,7 +1952,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1967,17 +1979,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2010,7 +2022,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A45" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A47" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -2981,13 +2993,27 @@
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="5"/>
+      <c r="B42" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" s="4">
+        <v>250</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46325</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" s="4">
+        <v>50</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="5">
+        <v>46325</v>
+      </c>
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2998,11 +3024,21 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F43" s="4">
+        <v>30</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H43" s="5">
+        <v>46325</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -3012,35 +3048,71 @@
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="5"/>
+      <c r="E44" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F44" s="4">
+        <v>120</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="5">
+        <v>46325</v>
+      </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>43</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="7">
-        <f>SUM(C3:C38)</f>
-        <v>5947</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="7">
-        <f>SUM(F3:F41)</f>
-        <v>4692</v>
-      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="5"/>
       <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <f>ROW()-2</f>
+        <v>44</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="7">
+        <f>SUM(C3:C38)</f>
+        <v>5947</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="7">
+        <f>SUM(F3:F44)</f>
+        <v>4892</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3068,16 +3140,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">

--- a/RC_FASTags_TransitStatus.xlsx
+++ b/RC_FASTags_TransitStatus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAC9F5-E0F4-49A1-9669-8656C405D553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65DB4D8-B949-4BBF-A5FB-299876B45F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="599" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="247">
   <si>
     <t>S.No.</t>
   </si>
@@ -747,13 +747,37 @@
     <t>540251 - 540500</t>
   </si>
   <si>
-    <t>540251 - 540300</t>
-  </si>
-  <si>
-    <t>540301 - 540330</t>
-  </si>
-  <si>
-    <t>540331 - 540500</t>
+    <t>SHAFKAT BARAMULLA</t>
+  </si>
+  <si>
+    <t>SRM</t>
+  </si>
+  <si>
+    <t>BARAMULLA</t>
+  </si>
+  <si>
+    <t>547001 - 547250</t>
+  </si>
+  <si>
+    <t>532501 - 532750</t>
+  </si>
+  <si>
+    <t>546501 - 546750</t>
+  </si>
+  <si>
+    <t>546751 - 547000</t>
+  </si>
+  <si>
+    <t>547751 - 548000</t>
+  </si>
+  <si>
+    <t>548001 - 548250</t>
+  </si>
+  <si>
+    <t>548251 - 548500</t>
+  </si>
+  <si>
+    <t>548501 - 548750</t>
   </si>
 </sst>
 </file>
@@ -880,13 +904,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1012,6 +1036,163 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1372,163 +1553,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1543,45 +1567,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I47" headerRowDxfId="56" dataDxfId="55">
-  <autoFilter ref="A2:I47" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I47">
-    <sortCondition ref="H2:H47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:I53" headerRowDxfId="66" dataDxfId="65">
+  <autoFilter ref="A2:I53" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I53">
+    <sortCondition ref="H2:H53"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="54" totalsRowDxfId="53">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="64" totalsRowDxfId="63">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="52" totalsRowDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="50" totalsRowDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="48" totalsRowDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="46" totalsRowDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="44" totalsRowDxfId="43"/>
-    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="40" totalsRowDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="38" totalsRowDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{41F3F928-C5F4-479D-8794-38082DFADE30}" name="Serial" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{6551D741-ECEA-463A-A282-9E465AC65D87}" name="RTO Rc Rec" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{27CFA8EB-0A9B-4187-B61B-83F48466BC43}" name="Date" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Card Number" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{00D6D077-3271-44BD-842C-3A558BFFF932}" name="Qty" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{2DE97642-A764-4067-B347-A03241193D5E}" name="Channel" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date2" dataDxfId="50" totalsRowDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="48" totalsRowDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:H63" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A2:H63" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H63">
     <sortCondition ref="D2:D63"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="44">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{64D5D4EA-324D-44CA-A67C-7C8E63C1A56D}" name="Order" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1952,7 +1976,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1979,17 +2003,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.75" x14ac:dyDescent="0.5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2022,7 +2046,7 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A47" si="0">ROW()-2</f>
+        <f t="shared" ref="A3:A53" si="0">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4"/>
@@ -3003,16 +3027,16 @@
         <v>46325</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F42" s="4">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H42" s="5">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="I42" s="4"/>
     </row>
@@ -3021,45 +3045,39 @@
         <f t="shared" si="4"/>
         <v>41</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="F43" s="4">
-        <v>30</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H43" s="5">
-        <v>46325</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>164</v>
-      </c>
+      <c r="B43" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" s="4">
+        <v>250</v>
+      </c>
+      <c r="D43" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f t="shared" si="4"/>
         <v>42</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F44" s="4">
-        <v>120</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="5">
-        <v>46325</v>
-      </c>
+      <c r="B44" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="4">
+        <v>250</v>
+      </c>
+      <c r="D44" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="5"/>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -3067,9 +3085,15 @@
         <f>ROW()-2</f>
         <v>43</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="5"/>
+      <c r="B45" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" s="4">
+        <v>250</v>
+      </c>
+      <c r="D45" s="5">
+        <v>46326</v>
+      </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -3081,9 +3105,15 @@
         <f>ROW()-2</f>
         <v>44</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="5"/>
+      <c r="B46" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C46" s="4">
+        <v>250</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46326</v>
+      </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -3092,27 +3122,135 @@
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
-        <f t="shared" si="0"/>
+        <f>ROW()-2</f>
         <v>45</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C47" s="7">
-        <f>SUM(C3:C38)</f>
-        <v>5947</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F47" s="7">
-        <f>SUM(F3:F44)</f>
-        <v>4892</v>
-      </c>
+      <c r="B47" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" s="4">
+        <v>250</v>
+      </c>
+      <c r="D47" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="5"/>
       <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <f>ROW()-2</f>
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" s="4">
+        <v>250</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <f>ROW()-2</f>
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C49" s="4">
+        <v>250</v>
+      </c>
+      <c r="D49" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <f>ROW()-2</f>
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="4">
+        <v>250</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46326</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <f>ROW()-2</f>
+        <v>49</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <f>ROW()-2</f>
+        <v>50</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="7">
+        <f>SUBTOTAL(109,C3:C52)</f>
+        <v>8197</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" s="7">
+        <f>SUBTOTAL(109,F3:F52)</f>
+        <v>4942</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3140,16 +3278,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -5426,10 +5564,18 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7889596663</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
